--- a/mistral_translate_work/split_by_prompt/excel/ui/lang_multi_text/lang_multi_text__ui__part_0010.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/ui/lang_multi_text/lang_multi_text__ui__part_0010.xlsx
@@ -1484,7 +1484,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Hàng Cung Ứng Special</t>
+          <t>Vật Tư Đặc Biệt</t>
         </is>
       </c>
     </row>
@@ -2004,7 +2004,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Details Exam</t>
+          <t>Chi Tiết Kỳ Thi</t>
         </is>
       </c>
     </row>
@@ -2589,7 +2589,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Đã hoàn thành</t>
         </is>
       </c>
     </row>
@@ -3174,7 +3174,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>Claimed</t>
+          <t>Đã nhận</t>
         </is>
       </c>
     </row>
@@ -3694,7 +3694,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>Claimed</t>
+          <t>Đã nhận</t>
         </is>
       </c>
     </row>
@@ -6489,7 +6489,7 @@
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>Switch</t>
+          <t>Chuyển đổi</t>
         </is>
       </c>
     </row>
@@ -6814,7 +6814,7 @@
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>Progress</t>
+          <t>Tiến độ</t>
         </is>
       </c>
     </row>
@@ -8244,7 +8244,7 @@
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>Ranking</t>
+          <t>Xếp hạng</t>
         </is>
       </c>
     </row>
@@ -9869,7 +9869,7 @@
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t>Ranking</t>
+          <t>Xếp hạng</t>
         </is>
       </c>
     </row>
@@ -10454,7 +10454,7 @@
       </c>
       <c r="M154" t="inlineStr">
         <is>
-          <t>Stats</t>
+          <t>Chỉ số</t>
         </is>
       </c>
     </row>
@@ -12014,7 +12014,7 @@
       </c>
       <c r="M178" t="inlineStr">
         <is>
-          <t>Off</t>
+          <t>Tắt</t>
         </is>
       </c>
     </row>
@@ -12534,7 +12534,7 @@
       </c>
       <c r="M186" t="inlineStr">
         <is>
-          <t>Filter</t>
+          <t>Bộ lọc</t>
         </is>
       </c>
     </row>
@@ -12859,7 +12859,7 @@
       </c>
       <c r="M191" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=Touch PC=Bấm Gamepad=press} để đóng</t>
+          <t>{Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} để đóng</t>
         </is>
       </c>
     </row>
@@ -17931,7 +17931,7 @@
       </c>
       <c r="M269" t="inlineStr">
         <is>
-          <t>Im lặng trải dài. Rồi...</t>
+          <t>Silence trải dài. Rồi...</t>
         </is>
       </c>
     </row>
@@ -18581,7 +18581,7 @@
       </c>
       <c r="M279" t="inlineStr">
         <is>
-          <t>Restart</t>
+          <t>Bắt đầu lại</t>
         </is>
       </c>
     </row>
@@ -20076,7 +20076,7 @@
       </c>
       <c r="M302" t="inlineStr">
         <is>
-          <t>Progress</t>
+          <t>Tiến độ</t>
         </is>
       </c>
     </row>
@@ -20401,7 +20401,7 @@
       </c>
       <c r="M307" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Đã hoàn thành</t>
         </is>
       </c>
     </row>
@@ -20466,7 +20466,7 @@
       </c>
       <c r="M308" t="inlineStr">
         <is>
-          <t>Claimed</t>
+          <t>Đã nhận</t>
         </is>
       </c>
     </row>
@@ -23066,7 +23066,7 @@
       </c>
       <c r="M348" t="inlineStr">
         <is>
-          <t>Progress</t>
+          <t>Tiến độ</t>
         </is>
       </c>
     </row>
@@ -24431,7 +24431,7 @@
       </c>
       <c r="M369" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=Chạm vào bất kỳ đâu PC=Nhấp bất kỳ đâu Gamepad=Nhấn bất kỳ nút nào} để đóng</t>
+          <t>{Cus:Ipt,Touch=Tap anywhere PC=Click anywhere Gamepad=Press any button} để đóng</t>
         </is>
       </c>
     </row>
@@ -24691,7 +24691,7 @@
       </c>
       <c r="M373" t="inlineStr">
         <is>
-          <t>Progress</t>
+          <t>Tiến độ</t>
         </is>
       </c>
     </row>
@@ -25146,7 +25146,7 @@
       </c>
       <c r="M380" t="inlineStr">
         <is>
-          <t>Activated</t>
+          <t>Đã kích hoạt</t>
         </is>
       </c>
     </row>
@@ -25536,7 +25536,7 @@
       </c>
       <c r="M386" t="inlineStr">
         <is>
-          <t>Claimed</t>
+          <t>Đã nhận</t>
         </is>
       </c>
     </row>
@@ -26316,7 +26316,7 @@
       </c>
       <c r="M398" t="inlineStr">
         <is>
-          <t>Progress</t>
+          <t>Tiến độ</t>
         </is>
       </c>
     </row>
@@ -26771,7 +26771,7 @@
       </c>
       <c r="M405" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=Vuốt màn hình PC=Kéo Gamepad=Rotate} để xoay Exostrider Component sao cho hình chiếu khớp với hoa văn trên tường</t>
+          <t>{Cus:Ipt,Touch=Swipe the screen to rotate the Exostrider Component PC=Drag to rotate the Exostrider Component Gamepad=Rotate the Exostrider Component} để xoay Exostrider Component sao cho hình chiếu khớp với hoa văn trên tường</t>
         </is>
       </c>
     </row>
@@ -26901,7 +26901,7 @@
       </c>
       <c r="M407" t="inlineStr">
         <is>
-          <t>Pioneer Association</t>
+          <t>Hiệp Hội Tiên Phong</t>
         </is>
       </c>
     </row>
@@ -27941,7 +27941,7 @@
       </c>
       <c r="M423" t="inlineStr">
         <is>
-          <t>Claimed</t>
+          <t>Đã nhận</t>
         </is>
       </c>
     </row>
@@ -28266,7 +28266,7 @@
       </c>
       <c r="M428" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=Chạm vào bất kỳ đâu PC=Nhấp bất kỳ đâu Gamepad=Nhấn bất kỳ nút nào} để đóng</t>
+          <t>{Cus:Ipt,Touch=Tap anywhere PC=Click anywhere Gamepad=Press any button} để đóng</t>
         </is>
       </c>
     </row>
@@ -28461,7 +28461,7 @@
       </c>
       <c r="M431" t="inlineStr">
         <is>
-          <t>Endstate Matrix</t>
+          <t>Ma Trận Endstate</t>
         </is>
       </c>
     </row>
@@ -28591,7 +28591,7 @@
       </c>
       <c r="M433" t="inlineStr">
         <is>
-          <t>Bức ảnh chụp tôi và Camellya ngắm sao tại địa điểm A</t>
+          <t>Bức ảnh chụp ta và Camellya ngắm sao ở địa điểm A.</t>
         </is>
       </c>
     </row>
@@ -28656,7 +28656,7 @@
       </c>
       <c r="M434" t="inlineStr">
         <is>
-          <t>Bức ảnh chụp tôi và Camellya ngắm trăng tại địa điểm B</t>
+          <t>Bức ảnh ta và Camellya ngắm trăng tại địa điểm B</t>
         </is>
       </c>
     </row>
@@ -28721,7 +28721,7 @@
       </c>
       <c r="M435" t="inlineStr">
         <is>
-          <t>Ảnh chụp tôi và Camellya ngắm biển tại địa điểm C</t>
+          <t>Bức ảnh chụp ta và Camellya ngắm biển ở địa điểm C.</t>
         </is>
       </c>
     </row>
@@ -28786,7 +28786,7 @@
       </c>
       <c r="M436" t="inlineStr">
         <is>
-          <t>Sách điện tử từ độc giả A và độc giả B</t>
+          <t>Sách điện tử do độc giả A và độc giả B tặng</t>
         </is>
       </c>
     </row>
@@ -28851,7 +28851,7 @@
       </c>
       <c r="M437" t="inlineStr">
         <is>
-          <t>Tác phẩm đã hoàn thành và cập nhật</t>
+          <t>Hoàn thành và cập nhật các tác phẩm</t>
         </is>
       </c>
     </row>
@@ -28916,7 +28916,7 @@
       </c>
       <c r="M438" t="inlineStr">
         <is>
-          <t>(Bài toán chữ) Theo hướng của Blake Bloom, câu trả lời cho điều cần khám phá sẽ được hé lộ.</t>
+          <t>(Câu đố chữ) Theo dấu Blake Bloom, câu trả lời cho điều cần khám phá sẽ được hé lộ.</t>
         </is>
       </c>
     </row>
@@ -28981,7 +28981,7 @@
       </c>
       <c r="M439" t="inlineStr">
         <is>
-          <t>Giống như lần trước thôi, Rover. Cậu biết tìm tôi ở đâu mà.</t>
+          <t>Giống như lần trước thôi, Rover. Cậu biết cách tìm tao mà.</t>
         </is>
       </c>
     </row>
@@ -29046,7 +29046,7 @@
       </c>
       <c r="M440" t="inlineStr">
         <is>
-          <t>Một tấm áp phích cũ được bảo quản rất tốt, mép giấy đã sờn nhưng vẫn còn thấy rõ dòng chữ đồ họa ở trung tâm.</t>
+          <t>Một tấm áp phích cũ được bảo quản khá tốt, mép giấy đã sờn nhưng dòng chữ đồ họa ở giữa vẫn còn rõ nét.</t>
         </is>
       </c>
     </row>
@@ -29111,7 +29111,7 @@
       </c>
       <c r="M441" t="inlineStr">
         <is>
-          <t>Bức ảnh chân thực này có thể gợi ý manh mối về kho báu ẩn quanh Whining Aix's Mire.</t>
+          <t>Bức ảnh chân thực này có thể gợi ý manh mối về kho báu ẩn giấu quanh Bãi Lầy Than Vãn của Aix.</t>
         </is>
       </c>
     </row>
@@ -29176,7 +29176,7 @@
       </c>
       <c r="M442" t="inlineStr">
         <is>
-          <t>Bức ảnh chân thực này có thể gợi ý manh mối về kho báu ẩn quanh Tiger's Maw.</t>
+          <t>Bức ảnh chân thực này có thể gợi ý manh mối về kho báu ẩn giấu quanh Hàm Hổ.</t>
         </is>
       </c>
     </row>
@@ -29241,7 +29241,7 @@
       </c>
       <c r="M443" t="inlineStr">
         <is>
-          <t>Bức ảnh chân thực này có thể gợi ý manh mối về kho báu ẩn quanh Khu Rừng Mù Sương.</t>
+          <t>Bức ảnh chân thực này có thể gợi ý manh mối về kho báu ẩn giấu quanh Khu Rừng Mờ.</t>
         </is>
       </c>
     </row>
@@ -29306,7 +29306,7 @@
       </c>
       <c r="M444" t="inlineStr">
         <is>
-          <t>Có vẻ như đám Hoochief trong hang đã quay về rừng rồi. Thôi thì, coi đây là khởi đầu mới cho cuộc sống tốt đẹp của chúng ta, hahaha!</t>
+          <t>Xem ra mấy ông Hoochief trong hang đã quay về rừng rồi. Thôi thì, coi đây là khởi đầu mới cho cuộc sống tốt đẹp nào, hahaha!</t>
         </is>
       </c>
     </row>
@@ -29436,7 +29436,7 @@
       </c>
       <c r="M446" t="inlineStr">
         <is>
-          <t>Biển cảnh báo trống trơn với thiết kế bị nước biển làm mờ đến mức không thể biết nó từng cảnh báo điều gì......</t>
+          <t>Biển báo trắng xóa, hoa văn bị nước biển ăn mòn đến mức không thể biết nó từng cảnh báo điều gì...</t>
         </is>
       </c>
     </row>
@@ -29501,7 +29501,7 @@
       </c>
       <c r="M447" t="inlineStr">
         <is>
-          <t>Trong thời gian nghỉ lễ, cửa hàng vẫn mở cửa kinh doanh như bình thường, rất hoan nghênh khách hàng mới và cũ đến thưởng thức.</t>
+          <t>Trong thời gian nghỉ lễ, cửa hàng vẫn mở cửa kinh doanh bình thường, rất hoan nghênh cả khách cũ lẫn khách mới đến thưởng thức.</t>
         </is>
       </c>
     </row>
@@ -29566,7 +29566,7 @@
       </c>
       <c r="M448" t="inlineStr">
         <is>
-          <t>Đừng để tay chạm vào điện, an toàn nằm trong suy nghĩ của bạn.</t>
+          <t>Đừng để tay dính điện, an toàn nằm trong suy nghĩ của cậu mà.</t>
         </is>
       </c>
     </row>
@@ -29632,8 +29632,8 @@
       </c>
       <c r="M449" t="inlineStr">
         <is>
-          <t>Nếu cậu là thứ gọi là "tàu vũ trụ" trong cuốn sách bố đọc cho tôi, hãy nói tên tôi với mẹ trên trời nhé!
-Tôi là Stargazer! "Ngôi sao" nơi mẹ ở!</t>
+          <t>Nếu cậu chính là thứ gọi là "tàu vũ trụ" trong cuốn sách bố đọc cho con, hãy nói tên con với mẹ trên trời nhé!
+Con tên là Stargazer! "Ngôi sao" nơi mẹ ở!</t>
         </is>
       </c>
     </row>
@@ -29699,8 +29699,8 @@
       </c>
       <c r="M450" t="inlineStr">
         <is>
-          <t>Hẹn gặp lại cậu vào lúc nào đó.
-Có lẽ là ngày cậu quên mất tên tôi.</t>
+          <t>Hẹn gặp lại cậu một ngày nào đó.
+Có khi là ngày cậu quên mất tên tớ ấy.</t>
         </is>
       </c>
     </row>
@@ -29766,8 +29766,8 @@
       </c>
       <c r="M451" t="inlineStr">
         <is>
-          <t>Kiểu dáng hầu như không còn nhận ra là loại tiền tệ từng tượng trưng cho sự giàu có.
-Gắn ở góc túi là một mảnh giấy ghi dòng chữ "Nước!"</t>
+          <t>Kiểu dáng này gần như không còn nhận ra là loại tiền tệ từng tượng trưng cho sự giàu sang nữa.
+Góc túi có gài một mảnh giấy ghi dòng chữ "Nước!"</t>
         </is>
       </c>
     </row>
@@ -29832,7 +29832,7 @@
       </c>
       <c r="M452" t="inlineStr">
         <is>
-          <t>“Ánh sáng sẽ không bao giờ tắt tại ngọn hải đăng. Bạn luôn được chào đón trở về nhà bất cứ lúc nào, người bạn ạ."</t>
+          <t>“Ánh sáng ở ngọn hải đăng sẽ không bao giờ tắt. Bạn luôn được chào đón trở về nhà, người bạn ơi.”</t>
         </is>
       </c>
     </row>
@@ -29963,8 +29963,8 @@
       </c>
       <c r="M454" t="inlineStr">
         <is>
-          <t>Bảng thông báo cũ
-Khu bảo tồn Heron Wetland phía trước. Vui lòng không trèo rào.</t>
+          <t>Bảng Thông Báo Phai Mờ
+Phía trước là Khu Bảo Tồn Đầm Lầy Heron. Xin đừng trèo rào.</t>
         </is>
       </c>
     </row>
@@ -30029,7 +30029,7 @@
       </c>
       <c r="M455" t="inlineStr">
         <is>
-          <t>"Ngọn hải đăng sẽ luôn tỏa sáng với ánh sáng vĩnh cửu. Chào mừng trở về, người bạn của tôi."</t>
+          <t>"Ngọn hải đăng sẽ luôn tỏa sáng ánh sáng vĩnh cửu. Chào mừng trở về, người bạn của ta."</t>
         </is>
       </c>
     </row>
@@ -30094,7 +30094,7 @@
       </c>
       <c r="M456" t="inlineStr">
         <is>
-          <t>...Hãy tăng cường thể lực và thường xuyên luyện tập nín thở dưới nước.</t>
+          <t>...Hãy rèn luyện thân thể và tập nín thở dưới nước thường xuyên đi.</t>
         </is>
       </c>
     </row>
@@ -30160,8 +30160,8 @@
       </c>
       <c r="M457" t="inlineStr">
         <is>
-          <t>Năm dấu hiệu hình như lồng giam, một trong số đó dường như chứa thứ gì đó đặc biệt.
-Về manh mối để mở khóa những chiếc lồng này, có lẽ hãy tìm những dấu hiệu khác thường...</t>
+          <t>Năm dấu hiệu hình lồng giam, trong đó có một cái dường như đang giam giữ thứ gì đó đặc biệt.
+Còn manh mối để mở khóa những chiếc lồng này, có lẽ nên tìm những dấu hiệu khác thường...</t>
         </is>
       </c>
     </row>
@@ -30226,7 +30226,7 @@
       </c>
       <c r="M458" t="inlineStr">
         <is>
-          <t>Bức thư ngắn ngủi kể về một gia đình nghèo mất đi người thân hết lần này đến lần khác, nhưng lại sở hữu của cải và sức mạnh của SHC (văn bản tạm thời).</t>
+          <t>lá thư ngắn ngủi kể về một gia đình nghèo liên tục mất đi người thân, nhưng lại có được sự giàu sang và sức mạnh của SHC (văn bản tạm thời)</t>
         </is>
       </c>
     </row>
@@ -30291,7 +30291,7 @@
       </c>
       <c r="M459" t="inlineStr">
         <is>
-          <t>con cừu đen, phù thủy, dị giáo, trục xuất cô ta (văn bản tạm thời).</t>
+          <t>kẻ lạc loài, phù thủy, dị giáo, hãy trục xuất cô ta</t>
         </is>
       </c>
     </row>
@@ -30356,7 +30356,7 @@
       </c>
       <c r="M460" t="inlineStr">
         <is>
-          <t>Đầu Cừu Đen, Máu Lợn, Thương Hiệu Thần Thánh, Củi Khô, Lương Tháng... (Bản sao tạm thời của copywriter)</t>
+          <t>Đầu Cừu Đen, Huyết Heo, Dấu Ấn Thần, Củi Khô, Lương Tháng... (Bản sao tạm thời)</t>
         </is>
       </c>
     </row>
@@ -30421,7 +30421,7 @@
       </c>
       <c r="M461" t="inlineStr">
         <is>
-          <t>Thần thật sự...... Không, đó là quỷ. Con quỷ đỏ đã giáng thế! Cứu tôi với!</t>
+          <t>Thần thật... Không, đó là ác quỷ. Ác quỷ đỏ đã giáng thế! Cứu tôi với!</t>
         </is>
       </c>
     </row>
@@ -30486,7 +30486,7 @@
       </c>
       <c r="M462" t="inlineStr">
         <is>
-          <t>Góc trên bên trái bản đồ có dấu hiệu nổi bật. Điều này có thể chỉ vị trí của câu đố.</t>
+          <t>Góc trên bên trái bản đồ có một điểm đánh dấu nổi bật. Có thể đó là vị trí của câu đố.</t>
         </is>
       </c>
     </row>
@@ -30551,7 +30551,7 @@
       </c>
       <c r="M463" t="inlineStr">
         <is>
-          <t>Page sách tranh bị rách</t>
+          <t>Trang Sách Tranh Rách</t>
         </is>
       </c>
     </row>
@@ -30617,7 +30617,7 @@
       </c>
       <c r="M464" t="inlineStr">
         <is>
-          <t>Trà tiếp sức hôm nay đã đến rồi. Cứ tự nhiên lấy nếu cần nhé.
+          <t>Trà tiếp tế hôm nay đã đến rồi. Cần thì cứ tự nhiên lấy nhé.
 Cảm ơn những người lao động chăm chỉ ở Jinzhou.</t>
         </is>
       </c>
@@ -30683,7 +30683,7 @@
       </c>
       <c r="M465" t="inlineStr">
         <is>
-          <t>Sôi động và sảng khoái! Hãy tiếp thêm năng lượng cho những ngày dài với thức uống điện giải được đồng phát triển bởi Huaxu Academy và Bộ Phát triển!</t>
+          <t>Tươi mát và sảng khoái! Hãy tiếp thêm năng lượng cho những ngày dài bằng thức uống điện giải do Học viện Huaxu và Bộ Phát triển hợp tác phát triển!</t>
         </is>
       </c>
     </row>
@@ -30748,7 +30748,7 @@
       </c>
       <c r="M466" t="inlineStr">
         <is>
-          <t>test/Dành cho mảnh ký ức rời rạc.</t>
+          <t>Dành cho mảnh truyện rời.</t>
         </is>
       </c>
     </row>
@@ -30813,7 +30813,7 @@
       </c>
       <c r="M467" t="inlineStr">
         <is>
-          <t>"Chờ đợi mạch truyện đứt đoạn."</t>
+          <t>chờ đợi mảnh truyện rời rạc."</t>
         </is>
       </c>
     </row>
@@ -30878,7 +30878,7 @@
       </c>
       <c r="M468" t="inlineStr">
         <is>
-          <t>"Chờ đợi mạch truyện đứt đoạn."</t>
+          <t>chờ đợi mảnh truyện rời rạc."</t>
         </is>
       </c>
     </row>
@@ -30943,7 +30943,7 @@
       </c>
       <c r="M469" t="inlineStr">
         <is>
-          <t>"Chờ đợi mạch truyện đứt đoạn."</t>
+          <t>chờ đợi mảnh truyện rời rạc."</t>
         </is>
       </c>
     </row>
@@ -31008,7 +31008,7 @@
       </c>
       <c r="M470" t="inlineStr">
         <is>
-          <t>Thí nghiệm thất bại, mục tiêu không đạt... Tôi chịu hết nổi rồi! Tôi chỉ muốn được lắng nghe...</t>
+          <t>Thí nghiệm thất bại, mục tiêu không đạt… Ta chịu hết nổi rồi! Ta chỉ muốn được lắng nghe thôi…</t>
         </is>
       </c>
     </row>
@@ -31073,7 +31073,7 @@
       </c>
       <c r="M471" t="inlineStr">
         <is>
-          <t>Tôi đã hứa với con trai mình sẽ chứng kiến sự thất bại của Ovathrax và nền hòa bình mà cậu ấy đã chiến đấu hết mình vì nó.</t>
+          <t>Tao đã hứa với con trai tao là sẽ chứng kiến sự thất bại của Ovathrax và hòa bình mà nó đã chiến đấu vì nó.</t>
         </is>
       </c>
     </row>
@@ -31138,7 +31138,7 @@
       </c>
       <c r="M472" t="inlineStr">
         <is>
-          <t>Nếu người ta muốn thức ăn, họ phải trả tiền. Nếu muốn được trả tiền, họ phải làm việc. Nhưng tôi thì sao, nếu thứ tôi muốn là BIẾT TẤT CẢ về thế giới này?</t>
+          <t>Nếu người ta muốn thức ăn, họ phải trả tiền. Nếu muốn được trả tiền, họ phải làm việc. Nhưng nếu thứ ta muốn là TẤT CẢ về thế giới này, thì ta phải làm gì đây?</t>
         </is>
       </c>
     </row>
@@ -31203,7 +31203,7 @@
       </c>
       <c r="M473" t="inlineStr">
         <is>
-          <t>Cha à, mong muốn của cha là gì? Giúp mọi người thực hiện ước mơ của họ sao?</t>
+          <t>Cha à, ước nguyện của cha là gì? Giúp mọi người thực hiện ước mơ của họ sao?</t>
         </is>
       </c>
     </row>
@@ -31268,7 +31268,7 @@
       </c>
       <c r="M474" t="inlineStr">
         <is>
-          <t>Trên những vách đá cao chót vót vươn lên trời, một con rồng thực sự xuất hiện từ trong mây.</t>
+          <t>Trên những vách đá cao chót vót vươn lên trời, một con rồng đích thực hiện ra từ trong mây.</t>
         </is>
       </c>
     </row>
@@ -31333,7 +31333,7 @@
       </c>
       <c r="M475" t="inlineStr">
         <is>
-          <t>Ánh đèn mờ ảo tỏa sáng dịu dàng trên mặt hồ khi tuyết rơi nhẹ từ bầu trời.</t>
+          <t>Ánh sáng mờ ảo phủ lên mặt hồ khi tuyết rơi nhẹ từ bầu trời.</t>
         </is>
       </c>
     </row>
@@ -31398,7 +31398,7 @@
       </c>
       <c r="M476" t="inlineStr">
         <is>
-          <t>Nước trong hồ sâu dường như ngưng tụ khi một lối vào hang động mở ra.</t>
+          <t>Nước trong hồ sâu dường như ngưng tụ lại khi lối vào hố sâu mở ra.</t>
         </is>
       </c>
     </row>
@@ -31463,7 +31463,7 @@
       </c>
       <c r="M477" t="inlineStr">
         <is>
-          <t>Tại rìa Núi Firmament, tiếng sóng vỗ vọng từ những tàn tích ven biển.</t>
+          <t>Bên rìa núi Firmament, tiếng vọng triều dâng từ những tàn tích ven biển.</t>
         </is>
       </c>
     </row>
@@ -31528,7 +31528,7 @@
       </c>
       <c r="M478" t="inlineStr">
         <is>
-          <t>Placeholder</t>
+          <t>Vị trí tạm</t>
         </is>
       </c>
     </row>
@@ -31593,7 +31593,7 @@
       </c>
       <c r="M479" t="inlineStr">
         <is>
-          <t>Placeholder</t>
+          <t>Vị trí tạm</t>
         </is>
       </c>
     </row>
@@ -31658,7 +31658,7 @@
       </c>
       <c r="M480" t="inlineStr">
         <is>
-          <t>Em nên đứng chính giữa để cúi chào cuối cùng.</t>
+          <t>Cậu nên đứng chính giữa để cúi chào cuối cùng đi.</t>
         </is>
       </c>
     </row>
@@ -31723,7 +31723,7 @@
       </c>
       <c r="M481" t="inlineStr">
         <is>
-          <t>Em nên đứng chính giữa để cúi chào cuối cùng.</t>
+          <t>Cậu nên đứng chính giữa để cúi chào cuối cùng đi.</t>
         </is>
       </c>
     </row>
@@ -31789,8 +31789,8 @@
       </c>
       <c r="M482" t="inlineStr">
         <is>
-          <t>…Hãy để lại hận thù của biển cả tại đây…
-Hãy rộng lượng và trao tặng quà cáp, và nó sẽ dẫn lối bạn… về nhà.</t>
+          <t>…Hãy để lại nỗi hận biển khơi nơi đây…
+Hãy rộng lượng và trao tặng quà cáp, rồi nó sẽ dẫn lối ngươi… về nhà.</t>
         </is>
       </c>
     </row>
@@ -31855,7 +31855,7 @@
       </c>
       <c r="M483" t="inlineStr">
         <is>
-          <t>Một tờ giấy ghi chú với các con số viết bằng hai kiểu chữ khác nhau. Dãy số mới nhất là 7364.</t>
+          <t>Một tờ ghi chú với các con số viết bằng hai kiểu chữ khác nhau. Dãy số gần nhất là 7364.</t>
         </is>
       </c>
     </row>
@@ -31920,7 +31920,7 @@
       </c>
       <c r="M484" t="inlineStr">
         <is>
-          <t>Một thiết bị tìm thấy trong mắt Void Storm, tỏa ra luồng khí bất an. Nó dường như liên quan đến sự cố của robot thăm dò.</t>
+          <t>Thiết bị tìm thấy trong mắt Bão Hư Không, tỏa ra luồng khí bất an. Dường như có liên kết với sự cố trục trặc của robot thăm dò.</t>
         </is>
       </c>
     </row>
@@ -31985,7 +31985,7 @@
       </c>
       <c r="M485" t="inlineStr">
         <is>
-          <t>Một bức ảnh của bạn, Mornye và Lynae dưới Mặt Trời New.</t>
+          <t>Bức ảnh chụp cậu, Mornye và Lynae dưới Ánh Mặt Trời Mới.</t>
         </is>
       </c>
     </row>
@@ -32050,7 +32050,7 @@
       </c>
       <c r="M486" t="inlineStr">
         <is>
-          <t>Một bức ảnh của bạn, Mornye và Lynae dưới Mặt Trời New.</t>
+          <t>Bức ảnh chụp cậu, Mornye và Lynae dưới Ánh Mặt Trời Mới.</t>
         </is>
       </c>
     </row>
@@ -32116,8 +32116,8 @@
       </c>
       <c r="M487" t="inlineStr">
         <is>
-          <t>Tớ về thăm ông nội vào kỳ nghỉ. Nhà ông ấy thì...
-...Never mind. Để tớ viết nốt khi về nhà vậy.</t>
+          <t>Kỳ nghỉ vừa rồi tớ có về thăm ông nội. Nhà ông ấy... 
+...Thôi, để tớ kể nốt khi về nhà vậy.</t>
         </is>
       </c>
     </row>
@@ -32183,8 +32183,8 @@
       </c>
       <c r="M488" t="inlineStr">
         <is>
-          <t>Với cô ấy, một ngày bình yên và dịu dàng như thế này đã là lý do đủ để ăn mừng.
-Vì vậy, cô ấy chọn dành ngày này bên những người bạn thân yêu nhất.</t>
+          <t>Với cô ấy, một ngày bình yên và dịu dàng như thế này đã là lý do đủ để ăn mừng rồi.
+Vậy nên cô chọn dành ngày ấy bên những người bạn thân thương nhất.</t>
         </is>
       </c>
     </row>
@@ -32250,8 +32250,8 @@
       </c>
       <c r="M489" t="inlineStr">
         <is>
-          <t>Với cô ấy, một ngày bình yên và dịu dàng như thế này đã là lý do đủ để ăn mừng.
-Vì vậy, cô ấy chọn dành ngày này bên những người bạn thân yêu nhất.</t>
+          <t>Với cô ấy, một ngày bình yên và dịu dàng như thế này đã là lý do đủ để ăn mừng rồi.
+Vậy nên cô chọn dành ngày ấy bên những người bạn thân thương nhất.</t>
         </is>
       </c>
     </row>
@@ -32316,7 +32316,7 @@
       </c>
       <c r="M490" t="inlineStr">
         <is>
-          <t>Sử dụng Spacetrek Observatory để phát tín hiệu điều khiển, điều chỉnh Mảng Dự Báo Bầu Trời nhằm tạo ra thời tiết mô phỏng trên khắp Lahai-Roi.</t>
+          <t>Dùng Đài Thiên Văn Spacetrek để phát tín hiệu điều khiển, điều chỉnh Mảng Dự Báo Bầu Trời nhằm tạo thời tiết mô phỏng trên toàn Lahai-Roi</t>
         </is>
       </c>
     </row>
@@ -32382,8 +32382,8 @@
       </c>
       <c r="M491" t="inlineStr">
         <is>
-          <t>Âm nhạc vẫn tiếp tục, và tấm màn đỏ thẫm lại một lần nữa được kéo lên.
-Trong vở kịch bất tận này, bạn không còn lựa chọn nào khác ngoài việc đồng hành cùng cô ấy, điệu nhảy nối tiếp điệu nhảy.</t>
+          <t>Âm nhạc vẫn tiếp tục, bức màn đỏ lại được kéo lên.
+Trong vở kịch không hồi kết này, ngươi không còn lựa chọn nào khác ngoài việc cùng nàng nhảy mãi, điệu này nối tiếp điệu kia.</t>
         </is>
       </c>
     </row>
@@ -32448,7 +32448,7 @@
       </c>
       <c r="M492" t="inlineStr">
         <is>
-          <t>Giữa rừng trúc xanh mướt, một lưỡi kiếm sát khí đang ẩn giấu.</t>
+          <t>Giữa rừng trúc xanh mướt, lưỡi kiếm sát khí vẫn ẩn mình.</t>
         </is>
       </c>
     </row>
@@ -32514,8 +32514,8 @@
       </c>
       <c r="M493" t="inlineStr">
         <is>
-          <t>Sức mạnh còn vương vấn của Lời Than tập trung tại đây, tái hiện lại những trận chiến đã qua.
-Những giấc mơ dang dở, những nỗi ám ảnh chưa buông… Chúng không phải là huyền thoại.</t>
+          <t>Sức mạnh còn sót lại của Vòng Lặp Tang Tóc tụ hội tại đây, tái hiện lại những trận chiến trong quá khứ.
+Những giấc mơ dang dở, những ám ảnh chưa giải quyết... Chúng không phải là huyền thoại.</t>
         </is>
       </c>
     </row>
@@ -32580,7 +32580,7 @@
       </c>
       <c r="M494" t="inlineStr">
         <is>
-          <t>Mọi điều bạn đã làm, thế giới sẽ mãi ghi nhớ.</t>
+          <t>Những gì cậu đã làm, thế giới sẽ mãi ghi nhớ.</t>
         </is>
       </c>
     </row>
@@ -32645,7 +32645,7 @@
       </c>
       <c r="M495" t="inlineStr">
         <is>
-          <t>Nơi đây giản dị và mộc mạc, mang đến chốn nghỉ ngơi tạm thời trong vòng luẩn quẩn của Lament.</t>
+          <t>Nơi đây giản dị và mộc mạc, mang đến chút nghỉ ngơi tạm thời trong vòng lặp Nỗi Bi Thương.</t>
         </is>
       </c>
     </row>
@@ -32710,7 +32710,7 @@
       </c>
       <c r="M496" t="inlineStr">
         <is>
-          <t>Nơi đây, những vòng lặp vô tận chồng chất lên nhau, và tiếng kêu của con người trở thành thức ăn cho Lament. Trong đống đổ nát của hỗn loạn, chỉ có Tower là lộ diện chân tướng...</t>
+          <t>Nơi đây, vòng lặp vô tận chồng chất lên nhau, tiếng khóc của con người trở thành thức ăn cho Lời Than Vãn. Trong đống đổ nát của hỗn mang, chỉ có Tháp mới phơi bày bộ mặt thật của mình...</t>
         </is>
       </c>
     </row>
@@ -32776,8 +32776,8 @@
       </c>
       <c r="M497" t="inlineStr">
         <is>
-          <t>Bên trong Neon Tower, cô rơi vào chiếc lồng do chính mình tạo ra.
-Có lẽ cô gái ấy chưa bao giờ thực sự rời xa quê hương, cũng như chưa bao giờ thoát khỏi quá khứ…</t>
+          <t>Bên trong Tháp Neon, cô gái đã tự nhốt mình vào chiếc lồng do chính tay mình tạo ra.
+Có lẽ cô chưa bao giờ thực sự rời xa quê hương, cũng như chưa bao giờ thoát khỏi quá khứ…</t>
         </is>
       </c>
     </row>
@@ -32842,7 +32842,7 @@
       </c>
       <c r="M498" t="inlineStr">
         <is>
-          <t>Chưa bao giờ thấy Honami im lặng như thế này… Chisa, cậu ở đâu rồi?</t>
+          <t>Chưa bao giờ thấy Honami im lặng như thế này… Chisa, cậu đang ở đâu?</t>
         </is>
       </c>
     </row>
@@ -32908,8 +32908,8 @@
       </c>
       <c r="M499" t="inlineStr">
         <is>
-          <t>Thành phố xa lạ đang trên bờ vực sụp đổ.
-Từ sâu thẳm ký ức, một lời thì thầm đau đớn, mơ hồ vang lên... Đây chính là Lament.</t>
+          <t>Thành phố xa lạ này đang chao đảo bên bờ vực sụp đổ.
+Từ sâu thẳm ký ức, một tiếng thì thầm đau đớn, mơ hồ vang lên... Đây chính là Lời Than Thở.</t>
         </is>
       </c>
     </row>
@@ -32974,7 +32974,7 @@
       </c>
       <c r="M500" t="inlineStr">
         <is>
-          <t>Những tiếng thở dài của người ấy vẫn còn vương vấn nơi đây. Ôi kẻ bị xiềng xích, ngươi có thể giãi bày nỗi sầu muộn vô tận này với ai?</t>
+          <t>Những tiếng thở dài của người ấy vẫn còn vương vấn nơi đây. Ôi người bị xiềng xích, ngươi có thể giãi bày nỗi sầu muộn này với ai đây?</t>
         </is>
       </c>
     </row>
